--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>빅스짐 청주고속터미널점</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bigsgymgagyeong@naver.com</t>
+          <t>brofitness2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-8896</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충청북도 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_cheongju/</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5266</v>
+        <v>612</v>
       </c>
       <c r="Q2" t="n">
-        <v>1266</v>
+        <v>855</v>
       </c>
       <c r="R2" t="n">
-        <v>6532</v>
+        <v>1467</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1689856448</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689856448</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>라인업1989 프리미엄 헬스&amp;PT</t>
+          <t>빅스짐 청주고속터미널점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lineup_1989@naver.com</t>
+          <t>bigsgymgagyeong@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1457-0376</t>
+          <t>0507-1364-8896</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 송화로 162 3층</t>
+          <t>충청북도 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lineup_1989</t>
+          <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>74</v>
+        <v>5267</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>1268</v>
       </c>
       <c r="R3" t="n">
-        <v>148</v>
+        <v>6535</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1378779223</t>
+          <t>1689856448</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1378779223</t>
+          <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>grasp1069@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1336-5246</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 강서로 110 3층</t>
+          <t>충청북도 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/grasp1069</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4669</v>
+        <v>3353</v>
       </c>
       <c r="Q4" t="n">
-        <v>1234</v>
+        <v>805</v>
       </c>
       <c r="R4" t="n">
-        <v>5903</v>
+        <v>4158</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1446407109</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446407109</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,34 +845,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>어센드핏 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>ascendfit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1353-2554</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충청북도 청주시 서원구 원흥로 17 3층</t>
+          <t>충청북도 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://blog.naver.com/ascendfit</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3760</v>
+        <v>750</v>
       </c>
       <c r="Q5" t="n">
-        <v>2025</v>
+        <v>291</v>
       </c>
       <c r="R5" t="n">
-        <v>5785</v>
+        <v>1041</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1575613936</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1575613936</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,34 +939,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>보떼짐 헬스&amp;PT 용암점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>beautegym1633@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1342-9698</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 307 4층</t>
+          <t>충청북도 청주시 상당구 중고개로141번길 13-10 동남지구 DN에듀탑빌딩 9층 보떼짐 헬스&amp;PT 용암점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://blog.naver.com/beautegym1633/224098449019</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>612</v>
+        <v>201</v>
       </c>
       <c r="Q6" t="n">
-        <v>873</v>
+        <v>585</v>
       </c>
       <c r="R6" t="n">
-        <v>1485</v>
+        <v>786</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>1214614211</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/1214614211</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,43 +1029,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>브로피트니스 복대점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>bro_sis_@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1447-7857</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충청북도 청주시 흥덕구 대농로 68 8층 브로피트니스 복대점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://www.instagram.com/bro__fitness3/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3352</v>
+        <v>608</v>
       </c>
       <c r="Q7" t="n">
-        <v>797</v>
+        <v>1591</v>
       </c>
       <c r="R7" t="n">
-        <v>4149</v>
+        <v>2199</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1717747911</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1717747911</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어센드핏 헬스&amp;PT</t>
+          <t>1대1 PT샵 드래곤짐 오송점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ascendfit@naver.com</t>
+          <t>dragongym-@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1353-2554</t>
+          <t>0507-1414-5644</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충청북도 청주시 흥덕구 오송읍 오송생명3로 65-15 4층 드래곤짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ascendfit</t>
+          <t>https://www.instagram.com/dragongym_osong</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1189,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="Q8" t="n">
-        <v>291</v>
+        <v>447</v>
       </c>
       <c r="R8" t="n">
-        <v>1041</v>
+        <v>507</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1575613936</t>
+          <t>1384370301</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575613936</t>
+          <t>https://m.place.naver.com/place/1384370301</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,30 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>보떼짐 헬스&amp;PT 용암점</t>
+          <t>레이크핏&amp;필라테스 오창점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>beautegym1633@naver.com</t>
+          <t>joysylee@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1320-3380</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로141번길 13-10 동남지구 DN에듀탑빌딩 9층 보떼짐 헬스&amp;PT 용암점</t>
+          <t>충청북도 청주시 청원구 오창읍 과학산업2로 363 신우에비뉴엘 빌딩 7층 레이크핏&amp;필라테스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beautegym1633/224098449019</t>
+          <t>https://www.instagram.com/lakefit_pilates</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="Q9" t="n">
-        <v>585</v>
+        <v>254</v>
       </c>
       <c r="R9" t="n">
-        <v>786</v>
+        <v>445</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1214614211</t>
+          <t>1741202578</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214614211</t>
+          <t>https://m.place.naver.com/place/1741202578</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,38 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐타이밍</t>
+          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymtiming1@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>jayoufree@gmail.com</t>
-        </is>
-      </c>
+          <t>cocofitness5@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>043-297-0220</t>
+          <t>0507-1428-5246</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충청북도 청주시 서원구 산남로70번길 34 7층</t>
+          <t>충청북도 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
+          <t>https://blog.naver.com/cocofitness5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>321</v>
+        <v>2654</v>
       </c>
       <c r="Q10" t="n">
-        <v>442</v>
+        <v>1495</v>
       </c>
       <c r="R10" t="n">
-        <v>763</v>
+        <v>4149</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13145981</t>
+          <t>1016038247</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13145981</t>
+          <t>https://m.place.naver.com/place/1016038247</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고트짐</t>
+          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goatgym@naver.com</t>
+          <t>grasp1069@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-1987</t>
+          <t>0507-1336-5246</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
+          <t>충청북도 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goatgym</t>
+          <t>https://blog.naver.com/grasp1069</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62</v>
+        <v>4670</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>1238</v>
       </c>
       <c r="R11" t="n">
-        <v>100</v>
+        <v>5908</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,15 +1482,955 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1290455974</t>
+          <t>1446407109</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
+          <t>https://m.place.naver.com/place/1446407109</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>오송헬스&amp;PT 다이아짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>top-health@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1354-1126</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 흥덕구 오송읍 오송생명로 185 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/top-health</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>4156</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2352</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6508</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1158935452</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1158935452</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>코코피트니스 헬스 PT 태닝 복대점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cocogym_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1443-0339</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 흥덕구 대농로 43 4층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@cocogym3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>3049</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1776</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4825</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1478272953</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1478272953</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>24시 코코피트니스 헬스 PT 필라테스 오송점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cocofitxx_pila7@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1446-5246</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 흥덕구 오송읍 오송생명11로 48 7층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cocofitxx_pila7/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1355</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1173</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2528</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1871844912</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1871844912</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>짐타워피트니스 24시헬스PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gymtower1@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1469-9049</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 상당구 수영로 285 튼튼타워 6층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymtower1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>2193</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>821</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3014</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1061323670</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1061323670</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cocogym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1354-0050</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 서원구 원흥로 17 3층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cocogym1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3760</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2028</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5788</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1286616507</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1286616507</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24시 코코피트니스 헬스 PT 율량점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jhh820116@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1377-5496</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coco_fitxx8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>297</v>
+      </c>
+      <c r="R17" t="n">
+        <v>522</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2051104888</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2051104888</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PT라운지 복대점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pt_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1408-0133</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 흥덕구 대농로 68 MJ트윈스빌딩 601호 PT라운지</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pt_lounge</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>948</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1396</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1945520016</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945520016</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>스마트짐 운천점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>smartgymblog@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1419-5331</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 흥덕구 사운로 245 2층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@TV-vi7rv</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>60</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2053593249</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053593249</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>브로피트니스 용암점 헬스장&amp;PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>whdgus1601@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1397-9698</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 상당구 1순환로 1247 4층 용암동 브로피트니스</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whdgus1601</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1228</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2459</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3687</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1769390027</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1769390027</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B.Y.GYM비와이짐</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>quddbs1540@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1482-8853</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>충청북도 청주시 상당구 산성로98번길 8 1층,2층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b.y.gym_by</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1068</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>94</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1162</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1407413991</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1407413991</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>빅스짐 청주고속터미널점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>bigsgymgagyeong@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1364-8896</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w456me</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>612</v>
+        <v>5289</v>
       </c>
       <c r="Q2" t="n">
-        <v>855</v>
+        <v>1287</v>
       </c>
       <c r="R2" t="n">
-        <v>1467</v>
+        <v>6576</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>1689856448</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>빅스짐 청주고속터미널점</t>
+          <t>휘트니스휴 동남지구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bigsgymgagyeong@naver.com</t>
+          <t>fithue9679@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1364-8896</t>
+          <t>0507-1357-9680</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충북 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_cheongju/</t>
+          <t>https://blog.naver.com/fithue9679</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4547b</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5267</v>
+        <v>872</v>
       </c>
       <c r="Q3" t="n">
-        <v>1268</v>
+        <v>618</v>
       </c>
       <c r="R3" t="n">
-        <v>6535</v>
+        <v>1490</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,55 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1689856448</t>
+          <t>1870900978</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689856448</t>
+          <t>https://m.place.naver.com/place/1870900978</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>라인업1989 프리미엄 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>lineup_1989@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1457-0376</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 흥덕구 송화로 162 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://blog.naver.com/lineup_1989</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pq0</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3353</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="n">
-        <v>805</v>
+        <v>74</v>
       </c>
       <c r="R4" t="n">
-        <v>4158</v>
+        <v>150</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1378779223</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1378779223</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>어센드핏 헬스&amp;PT</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ascendfit@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1353-2554</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ascendfit</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4otcd</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>750</v>
+        <v>3758</v>
       </c>
       <c r="Q5" t="n">
-        <v>291</v>
+        <v>2059</v>
       </c>
       <c r="R5" t="n">
-        <v>1041</v>
+        <v>5817</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,47 +934,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1575613936</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575613936</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보떼짐 헬스&amp;PT 용암점</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>beautegym1633@naver.com</t>
+          <t>brofitness2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1342-9698</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로141번길 13-10 동남지구 DN에듀탑빌딩 9층 보떼짐 헬스&amp;PT 용암점</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beautegym1633/224098449019</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d52a</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>201</v>
+        <v>614</v>
       </c>
       <c r="Q6" t="n">
-        <v>585</v>
+        <v>813</v>
       </c>
       <c r="R6" t="n">
-        <v>786</v>
+        <v>1427</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1214614211</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214614211</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브로피트니스 복대점 헬스&amp;PT</t>
+          <t>어센드핏 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bro_sis_@naver.com</t>
+          <t>ascendfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1447-7857</t>
+          <t>0507-1353-2554</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 대농로 68 8층 브로피트니스 복대점</t>
+          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bro__fitness3/</t>
+          <t>https://blog.naver.com/ascendfit</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjtwubz</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>608</v>
+        <v>761</v>
       </c>
       <c r="Q7" t="n">
-        <v>1591</v>
+        <v>294</v>
       </c>
       <c r="R7" t="n">
-        <v>2199</v>
+        <v>1055</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1717747911</t>
+          <t>1575613936</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717747911</t>
+          <t>https://m.place.naver.com/place/1575613936</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1대1 PT샵 드래곤짐 오송점</t>
+          <t>24시 코코피트니스 헬스 PT 율량점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dragongym-@naver.com</t>
+          <t>shaminwoo@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1414-5644</t>
+          <t>0507-1377-5496</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 오송읍 오송생명3로 65-15 4층 드래곤짐</t>
+          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dragongym_osong</t>
+          <t>https://www.instagram.com/coco_fitxx8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy2mfy3</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>60</v>
+        <v>274</v>
       </c>
       <c r="Q8" t="n">
-        <v>447</v>
+        <v>334</v>
       </c>
       <c r="R8" t="n">
-        <v>507</v>
+        <v>608</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1384370301</t>
+          <t>2051104888</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1384370301</t>
+          <t>https://m.place.naver.com/place/2051104888</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>레이크핏&amp;필라테스 오창점</t>
+          <t>닥터짐가경점 스피닝 TRX 개인PT 재활 체형교정</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>joysylee@naver.com</t>
+          <t>dr_gym_one@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1320-3380</t>
+          <t>0507-1397-7719</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충청북도 청주시 청원구 오창읍 과학산업2로 363 신우에비뉴엘 빌딩 7층 레이크핏&amp;필라테스</t>
+          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lakefit_pilates</t>
+          <t>https://blog.naver.com/dr_gym_one</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc42n5</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="Q9" t="n">
-        <v>254</v>
+        <v>497</v>
       </c>
       <c r="R9" t="n">
-        <v>445</v>
+        <v>783</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1741202578</t>
+          <t>31694969</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741202578</t>
+          <t>https://m.place.naver.com/place/31694969</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
+          <t>네오바디짐 율량점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cocofitness5@naver.com</t>
+          <t>neobodygym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1428-5246</t>
+          <t>0507-1314-5116</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
+          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocofitness5</t>
+          <t>https://blog.naver.com/neobodygym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy4h5jc</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2654</v>
+        <v>114</v>
       </c>
       <c r="Q10" t="n">
-        <v>1495</v>
+        <v>59</v>
       </c>
       <c r="R10" t="n">
-        <v>4149</v>
+        <v>173</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1016038247</t>
+          <t>2045981331</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016038247</t>
+          <t>https://m.place.naver.com/place/2045981331</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
+          <t>고트짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>grasp1069@naver.com</t>
+          <t>goatgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1336-5246</t>
+          <t>0507-1465-1987</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 강서로 110 3층</t>
+          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/grasp1069</t>
+          <t>https://blog.naver.com/goatgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,10 +1488,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vonm</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4670</v>
+        <v>64</v>
       </c>
       <c r="Q11" t="n">
-        <v>1238</v>
+        <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>5908</v>
+        <v>102</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1446407109</t>
+          <t>1290455974</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446407109</t>
+          <t>https://m.place.naver.com/place/1290455974</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오송헬스&amp;PT 다이아짐</t>
+          <t>쌍둥이휘트니스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>top-health@naver.com</t>
+          <t>ssangdoonge00072@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1354-1126</t>
+          <t>0507-1380-4951</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 오송읍 오송생명로 185 2층</t>
+          <t>충북 청주시 흥덕구 1순환로 606 바이크짱 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/top-health</t>
+          <t>https://www.instagram.com/ssangdungi_fitness/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,15 +1581,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41si2</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4156</v>
+        <v>162</v>
       </c>
       <c r="Q12" t="n">
-        <v>2352</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
-        <v>6508</v>
+        <v>178</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,863 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1158935452</t>
+          <t>37435004</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158935452</t>
+          <t>https://m.place.naver.com/place/37435004</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>코코피트니스 헬스 PT 태닝 복대점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>cocogym_3@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1443-0339</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 흥덕구 대농로 43 4층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@cocogym3</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>3049</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1776</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4825</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1478272953</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1478272953</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>24시 코코피트니스 헬스 PT 필라테스 오송점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>cocofitxx_pila7@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1446-5246</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 흥덕구 오송읍 오송생명11로 48 7층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/cocofitxx_pila7/</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1355</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1173</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2528</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1871844912</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1871844912</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>짐타워피트니스 24시헬스PT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>gymtower1@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1469-9049</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 상당구 수영로 285 튼튼타워 6층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/gymtower1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>2193</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>821</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3014</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1061323670</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1061323670</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>cocogym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1354-0050</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 서원구 원흥로 17 3층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/cocogym1</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3760</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2028</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5788</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1286616507</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24시 코코피트니스 헬스 PT 율량점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>jhh820116@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1377-5496</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/coco_fitxx8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>225</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>297</v>
-      </c>
-      <c r="R17" t="n">
-        <v>522</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2051104888</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2051104888</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PT라운지 복대점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pt_lounge@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1408-0133</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 흥덕구 대농로 68 MJ트윈스빌딩 601호 PT라운지</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pt_lounge</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>448</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>948</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1396</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1945520016</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1945520016</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>스마트짐 운천점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>smartgymblog@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1419-5331</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 흥덕구 사운로 245 2층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@TV-vi7rv</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10</v>
-      </c>
-      <c r="R19" t="n">
-        <v>60</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2053593249</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2053593249</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>브로피트니스 용암점 헬스장&amp;PT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>whdgus1601@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1397-9698</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 상당구 1순환로 1247 4층 용암동 브로피트니스</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/whdgus1601</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1228</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2459</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3687</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1769390027</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1769390027</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>B.Y.GYM비와이짐</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>quddbs1540@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1482-8853</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 상당구 산성로98번길 8 1층,2층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/b.y.gym_by</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1068</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>94</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1162</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1407413991</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1407413991</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>빅스짐 청주고속터미널점</t>
+          <t>휘트니스휴 동남지구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bigsgymgagyeong@naver.com</t>
+          <t>fithue9679@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-8896</t>
+          <t>0507-1357-9680</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충북 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_cheongju/</t>
+          <t>https://blog.naver.com/fithue9679</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w456me</t>
+          <t>https://talk.naver.com/ct/w4547b</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5289</v>
+        <v>874</v>
       </c>
       <c r="Q2" t="n">
-        <v>1287</v>
+        <v>618</v>
       </c>
       <c r="R2" t="n">
-        <v>6576</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1689856448</t>
+          <t>1870900978</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689856448</t>
+          <t>https://m.place.naver.com/place/1870900978</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>휘트니스휴 동남지구점</t>
+          <t>라인업1989 프리미엄 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fithue9679@naver.com</t>
+          <t>lineup_1989@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1357-9680</t>
+          <t>0507-1457-0376</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 호미로 3 4층</t>
+          <t>충북 청주시 흥덕구 송화로 162 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fithue9679</t>
+          <t>https://blog.naver.com/lineup_1989</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4547b</t>
+          <t>https://talk.naver.com/ct/w40pq0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>872</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="n">
-        <v>618</v>
+        <v>74</v>
       </c>
       <c r="R3" t="n">
-        <v>1490</v>
+        <v>150</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1870900978</t>
+          <t>1378779223</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870900978</t>
+          <t>https://m.place.naver.com/place/1378779223</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>라인업1989 프리미엄 헬스&amp;PT</t>
+          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lineup_1989@naver.com</t>
+          <t>grasp1069@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1457-0376</t>
+          <t>0507-1336-5246</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 송화로 162 3층</t>
+          <t>충북 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lineup_1989</t>
+          <t>https://blog.naver.com/grasp1069</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40pq0</t>
+          <t>https://talk.naver.com/ct/w4d0wj</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>76</v>
+        <v>4752</v>
       </c>
       <c r="Q4" t="n">
-        <v>74</v>
+        <v>1281</v>
       </c>
       <c r="R4" t="n">
-        <v>150</v>
+        <v>6033</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1378779223</t>
+          <t>1446407109</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1378779223</t>
+          <t>https://m.place.naver.com/place/1446407109</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
         <v>3758</v>
       </c>
       <c r="Q5" t="n">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="R5" t="n">
-        <v>5817</v>
+        <v>5822</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1020,10 @@
         <v>614</v>
       </c>
       <c r="Q6" t="n">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="R6" t="n">
-        <v>1427</v>
+        <v>1437</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>어센드핏 헬스&amp;PT</t>
+          <t>빅스짐 청주고속터미널점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ascendfit@naver.com</t>
+          <t>bigsgymgagyeong@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1353-2554</t>
+          <t>0507-1364-8896</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ascendfit</t>
+          <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjtwubz</t>
+          <t>https://talk.naver.com/ct/w456me</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>761</v>
+        <v>5304</v>
       </c>
       <c r="Q7" t="n">
-        <v>294</v>
+        <v>1288</v>
       </c>
       <c r="R7" t="n">
-        <v>1055</v>
+        <v>6592</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1575613936</t>
+          <t>1689856448</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575613936</t>
+          <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스 PT 율량점</t>
+          <t>어센드핏 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shaminwoo@naver.com</t>
+          <t>ascendfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1377-5496</t>
+          <t>0507-1353-2554</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
+          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coco_fitxx8</t>
+          <t>https://blog.naver.com/ascendfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy2mfy3</t>
+          <t>https://talk.naver.com/ct/wjtwubz</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>274</v>
+        <v>764</v>
       </c>
       <c r="Q8" t="n">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="R8" t="n">
-        <v>608</v>
+        <v>1058</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2051104888</t>
+          <t>1575613936</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051104888</t>
+          <t>https://m.place.naver.com/place/1575613936</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q9" t="n">
         <v>497</v>
       </c>
       <c r="R9" t="n">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네오바디짐 율량점 헬스 PT</t>
+          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>neobodygym@naver.com</t>
+          <t>cocofitness5@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-5116</t>
+          <t>0507-1428-5246</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
+          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/neobodygym</t>
+          <t>https://blog.naver.com/cocofitness5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy4h5jc</t>
+          <t>https://talk.naver.com/ct/w4h162</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>114</v>
+        <v>2660</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>1533</v>
       </c>
       <c r="R10" t="n">
-        <v>173</v>
+        <v>4193</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2045981331</t>
+          <t>1016038247</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045981331</t>
+          <t>https://m.place.naver.com/place/1016038247</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1446,34 +1446,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고트짐</t>
+          <t>짐타이밍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goatgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>gymtiming1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>jayoufree@gmail.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-1987</t>
+          <t>043-297-0220</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
+          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goatgym</t>
+          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1483,7 +1487,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vonm</t>
+          <t>https://talk.naver.com/ct/w4dqvo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>442</v>
       </c>
       <c r="R11" t="n">
-        <v>102</v>
+        <v>768</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1526,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1290455974</t>
+          <t>13145981</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
+          <t>https://m.place.naver.com/place/13145981</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1544,29 +1548,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>쌍둥이휘트니스</t>
+          <t>고트짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ssangdoonge00072@naver.com</t>
+          <t>goatgym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1380-4951</t>
+          <t>0507-1465-1987</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 1순환로 606 바이크짱 2층</t>
+          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssangdungi_fitness/</t>
+          <t>https://blog.naver.com/goatgym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1581,7 +1585,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1591,7 +1595,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41si2</t>
+          <t>https://talk.naver.com/ct/w5vonm</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1605,13 +1609,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="R12" t="n">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,17 +1624,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37435004</t>
+          <t>1290455974</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37435004</t>
+          <t>https://m.place.naver.com/place/1290455974</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 호미로 3 4층</t>
+          <t>충청북도 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4547b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 송화로 162 3층</t>
+          <t>충청북도 청주시 흥덕구 송화로 162 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40pq0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 강서로 110 3층</t>
+          <t>충청북도 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4d0wj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충청북도 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충청북도 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1000,10 @@
         <v>614</v>
       </c>
       <c r="Q6" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="R6" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충청북도 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w456me</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>5304</v>
+        <v>5306</v>
       </c>
       <c r="Q7" t="n">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="R7" t="n">
-        <v>6592</v>
+        <v>6595</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충청북도 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjtwubz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1267,7 +1239,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
+          <t>충청북도 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1292,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc42n5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,7 +1333,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
+          <t>충청북도 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h162</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="Q10" t="n">
         <v>1533</v>
       </c>
       <c r="R10" t="n">
-        <v>4193</v>
+        <v>4194</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1446,38 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐타이밍</t>
+          <t>네오바디짐 율량점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymtiming1@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>jayoufree@gmail.com</t>
-        </is>
-      </c>
+          <t>neobodygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>043-297-0220</t>
+          <t>0507-1314-5116</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
+          <t>충청북도 청주시 청원구 사뜸로 70 상가동 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
+          <t>https://blog.naver.com/neobodygym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1487,19 +1447,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqvo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1511,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>326</v>
+        <v>118</v>
       </c>
       <c r="Q11" t="n">
-        <v>442</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>768</v>
+        <v>180</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13145981</t>
+          <t>2045981331</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13145981</t>
+          <t>https://m.place.naver.com/place/2045981331</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1548,29 +1504,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>고트짐</t>
+          <t>짐타이밍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goatgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>gymtiming1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jayoufree@gmail.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1465-1987</t>
+          <t>043-297-0220</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
+          <t>충청북도 청주시 서원구 산남로70번길 34 7층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goatgym</t>
+          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1585,19 +1545,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vonm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1609,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="Q12" t="n">
-        <v>38</v>
+        <v>442</v>
       </c>
       <c r="R12" t="n">
-        <v>102</v>
+        <v>768</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1624,12 +1580,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1290455974</t>
+          <t>13145981</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
+          <t>https://m.place.naver.com/place/13145981</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 호미로 3 4층</t>
+          <t>충북 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4547b</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="Q2" t="n">
         <v>618</v>
       </c>
       <c r="R2" t="n">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 송화로 162 3층</t>
+          <t>충북 청주시 흥덕구 송화로 162 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pq0</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 강서로 110 3층</t>
+          <t>충북 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d0wj</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4752</v>
+        <v>4761</v>
       </c>
       <c r="Q4" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="R4" t="n">
-        <v>6033</v>
+        <v>6043</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충청북도 청주시 서원구 원흥로 17 3층</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4otcd</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -906,10 +922,10 @@
         <v>3758</v>
       </c>
       <c r="Q5" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="R5" t="n">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d52a</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w456me</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>5306</v>
+        <v>5307</v>
       </c>
       <c r="Q7" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="R7" t="n">
-        <v>6595</v>
+        <v>6597</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1145,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjtwubz</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1239,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
+          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc42n5</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
+          <t>퍼스트피지오 짐 PT 오송</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cocofitness5@naver.com</t>
+          <t>hongwoongpyo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1428-5246</t>
+          <t>0507-1348-2145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충청북도 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명8로 169 5층 501호~504호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocofitness5</t>
+          <t>https://www.instagram.com/1physio_gym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,15 +1385,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42rs0</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2661</v>
+        <v>214</v>
       </c>
       <c r="Q10" t="n">
-        <v>1533</v>
+        <v>259</v>
       </c>
       <c r="R10" t="n">
-        <v>4194</v>
+        <v>473</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1016038247</t>
+          <t>1247990748</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016038247</t>
+          <t>https://m.place.naver.com/place/1247990748</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1446,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네오바디짐 율량점 헬스 PT</t>
+          <t>짐타이밍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>neobodygym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>gymtiming1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>jayoufree@gmail.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-5116</t>
+          <t>043-297-0220</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충청북도 청주시 청원구 사뜸로 70 상가동 지하1층</t>
+          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/neobodygym</t>
+          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1487,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqvo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>118</v>
+        <v>326</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>442</v>
       </c>
       <c r="R11" t="n">
-        <v>180</v>
+        <v>768</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,113 +1526,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2045981331</t>
+          <t>13145981</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045981331</t>
+          <t>https://m.place.naver.com/place/13145981</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>짐타이밍</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>gymtiming1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jayoufree@gmail.com</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>043-297-0220</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>충청북도 청주시 서원구 산남로70번길 34 7층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>442</v>
-      </c>
-      <c r="R12" t="n">
-        <v>768</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>13145981</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/13145981</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>grasp1069@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1336-5246</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충북 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://blog.naver.com/grasp1069</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
+          <t>https://talk.naver.com/ct/w4d0wj</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3758</v>
+        <v>4766</v>
       </c>
       <c r="Q4" t="n">
-        <v>2067</v>
+        <v>1283</v>
       </c>
       <c r="R4" t="n">
-        <v>5825</v>
+        <v>6049</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1446407109</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1446407109</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>메이져복싱 테크노폴리스점</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gee2837@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>043-218-2245</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 송화로 182 6층</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gee2837</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vklw</t>
+          <t>https://talk.naver.com/ct/w4otcd</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>77</v>
+        <v>3758</v>
       </c>
       <c r="Q5" t="n">
-        <v>213</v>
+        <v>2067</v>
       </c>
       <c r="R5" t="n">
-        <v>290</v>
+        <v>5825</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>32618051</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32618051</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충청북도 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1096,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w456me</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="Q7" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="R7" t="n">
-        <v>6599</v>
+        <v>6601</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1446,33 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>네오바디짐 율량점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>neobodygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1314-5116</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://blog.naver.com/neobodygym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1487,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1497,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/wy4h5jc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1511,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3355</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="n">
-        <v>852</v>
+        <v>63</v>
       </c>
       <c r="R11" t="n">
-        <v>4207</v>
+        <v>183</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>2045981331</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/2045981331</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1637,202 +1629,6 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>고트짐</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>goatgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1465-1987</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/goatgym</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vonm</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>38</v>
-      </c>
-      <c r="R13" t="n">
-        <v>102</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1290455974</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>네오바디짐 율량점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>neobodygym@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1314-5116</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/neobodygym</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wy4h5jc</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>63</v>
-      </c>
-      <c r="R14" t="n">
-        <v>183</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2045981331</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2045981331</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -423,11 +423,11 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="Q2" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="R2" t="n">
-        <v>6604</v>
+        <v>6606</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Q3" t="n">
         <v>618</v>
       </c>
       <c r="R3" t="n">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         <v>4767</v>
       </c>
       <c r="Q5" t="n">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="R5" t="n">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>615</v>
       </c>
       <c r="Q6" t="n">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="R6" t="n">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>764</v>
       </c>
       <c r="Q7" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R7" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1348,33 +1348,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐타이밍</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymtiming1@naver.com</t>
+          <t>cookiegym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jayoufree@gmail.com</t>
+          <t>gotz6170@gmail.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>043-297-0220</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dqvo</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>327</v>
+        <v>3354</v>
       </c>
       <c r="Q10" t="n">
-        <v>442</v>
+        <v>852</v>
       </c>
       <c r="R10" t="n">
-        <v>769</v>
+        <v>4206</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13145981</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13145981</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="Q2" t="n">
         <v>1294</v>
       </c>
       <c r="R2" t="n">
-        <v>6606</v>
+        <v>6608</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4767</v>
+        <v>4769</v>
       </c>
       <c r="Q5" t="n">
         <v>1290</v>
       </c>
       <c r="R5" t="n">
-        <v>6057</v>
+        <v>6059</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,41 +944,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
+          <t>https://talk.naver.com/ct/w4otcd</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>615</v>
+        <v>3758</v>
       </c>
       <c r="Q6" t="n">
-        <v>835</v>
+        <v>2073</v>
       </c>
       <c r="R6" t="n">
-        <v>1450</v>
+        <v>5831</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>어센드핏 헬스&amp;PT</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ascendfit@naver.com</t>
+          <t>brofitness2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1353-2554</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ascendfit</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjtwubz</t>
+          <t>https://talk.naver.com/ct/w4d52a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>764</v>
+        <v>616</v>
       </c>
       <c r="Q7" t="n">
-        <v>293</v>
+        <v>835</v>
       </c>
       <c r="R7" t="n">
-        <v>1057</v>
+        <v>1451</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1575613936</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575613936</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>닥터짐가경점 스피닝 TRX 개인PT 재활 체형교정</t>
+          <t>어센드핏 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dr_gym_one@naver.com</t>
+          <t>ascendfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1397-7719</t>
+          <t>0507-1353-2554</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
+          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dr_gym_one</t>
+          <t>https://blog.naver.com/ascendfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc42n5</t>
+          <t>https://talk.naver.com/ct/wjtwubz</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>290</v>
+        <v>765</v>
       </c>
       <c r="Q8" t="n">
-        <v>498</v>
+        <v>293</v>
       </c>
       <c r="R8" t="n">
-        <v>788</v>
+        <v>1058</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>31694969</t>
+          <t>1575613936</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31694969</t>
+          <t>https://m.place.naver.com/place/1575613936</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>퍼스트피지오 짐 PT 오송</t>
+          <t>닥터짐가경점 스피닝 TRX 개인PT 재활 체형교정</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hongwoongpyo@naver.com</t>
+          <t>dr_gym_one@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1348-2145</t>
+          <t>0507-1397-7719</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명8로 169 5층 501호~504호</t>
+          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1physio_gym</t>
+          <t>https://blog.naver.com/dr_gym_one</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42rs0</t>
+          <t>https://talk.naver.com/ct/wc42n5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="Q9" t="n">
-        <v>260</v>
+        <v>498</v>
       </c>
       <c r="R9" t="n">
-        <v>475</v>
+        <v>789</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,55 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1247990748</t>
+          <t>31694969</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247990748</t>
+          <t>https://m.place.naver.com/place/31694969</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>퍼스트피지오 짐 PT 오송</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>hongwoongpyo@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1348-2145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명8로 169 5층 501호~504호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://www.instagram.com/1physio_gym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1399,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/w42rs0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3354</v>
+        <v>215</v>
       </c>
       <c r="Q10" t="n">
-        <v>852</v>
+        <v>260</v>
       </c>
       <c r="R10" t="n">
-        <v>4206</v>
+        <v>475</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1247990748</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1247990748</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1450,93 +1446,297 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고트짐</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goatgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-1987</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3354</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>855</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4209</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1245970521</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1245970521</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐타이밍</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gymtiming1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jayoufree@gmail.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>043-297-0220</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqvo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>442</v>
+      </c>
+      <c r="R12" t="n">
+        <v>769</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13145981</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13145981</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>고트짐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goatgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1465-1987</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://blog.naver.com/goatgym</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5vonm</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>64</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" t="n">
         <v>38</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>102</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>1290455974</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1290455974</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_PT.xlsx
+++ b/naver-place-crawler/results_health/청주_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -922,10 +922,10 @@
         <v>4769</v>
       </c>
       <c r="Q5" t="n">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="R5" t="n">
-        <v>6059</v>
+        <v>6060</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -951,34 +951,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>brofitness2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
+          <t>https://talk.naver.com/ct/w4d52a</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3758</v>
+        <v>616</v>
       </c>
       <c r="Q6" t="n">
-        <v>2073</v>
+        <v>835</v>
       </c>
       <c r="R6" t="n">
-        <v>5831</v>
+        <v>1451</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>어센드핏 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>ascendfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1353-2554</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://blog.naver.com/ascendfit</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
+          <t>https://talk.naver.com/ct/wjtwubz</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>616</v>
+        <v>765</v>
       </c>
       <c r="Q7" t="n">
-        <v>835</v>
+        <v>293</v>
       </c>
       <c r="R7" t="n">
-        <v>1451</v>
+        <v>1058</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>1575613936</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/1575613936</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어센드핏 헬스&amp;PT</t>
+          <t>닥터짐가경점 스피닝 TRX 개인PT 재활 체형교정</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ascendfit@naver.com</t>
+          <t>dr_gym_one@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1353-2554</t>
+          <t>0507-1397-7719</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 129 7층 703호</t>
+          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ascendfit</t>
+          <t>https://blog.naver.com/dr_gym_one</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjtwubz</t>
+          <t>https://talk.naver.com/ct/wc42n5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>765</v>
+        <v>291</v>
       </c>
       <c r="Q8" t="n">
-        <v>293</v>
+        <v>498</v>
       </c>
       <c r="R8" t="n">
-        <v>1058</v>
+        <v>789</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1575613936</t>
+          <t>31694969</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575613936</t>
+          <t>https://m.place.naver.com/place/31694969</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>닥터짐가경점 스피닝 TRX 개인PT 재활 체형교정</t>
+          <t>퍼스트피지오 짐 PT 오송</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dr_gym_one@naver.com</t>
+          <t>hongwoongpyo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1397-7719</t>
+          <t>0507-1348-2145</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 가경로 8-1 태경빌딩 9층</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명8로 169 5층 501호~504호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dr_gym_one</t>
+          <t>https://www.instagram.com/1physio_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc42n5</t>
+          <t>https://talk.naver.com/ct/w42rs0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="Q9" t="n">
-        <v>498</v>
+        <v>260</v>
       </c>
       <c r="R9" t="n">
-        <v>789</v>
+        <v>475</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>31694969</t>
+          <t>1247990748</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31694969</t>
+          <t>https://m.place.naver.com/place/1247990748</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>퍼스트피지오 짐 PT 오송</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hongwoongpyo@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1348-2145</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명8로 169 5층 501호~504호</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1physio_gym</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42rs0</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>215</v>
+        <v>3354</v>
       </c>
       <c r="Q10" t="n">
-        <v>260</v>
+        <v>855</v>
       </c>
       <c r="R10" t="n">
-        <v>475</v>
+        <v>4209</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1247990748</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247990748</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,38 +1450,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>짐타이밍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
+          <t>gymtiming1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>gotz6170@gmail.com</t>
+          <t>jayoufree@gmail.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>043-297-0220</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1497,7 +1501,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/w4dqvo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1511,13 +1515,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3354</v>
+        <v>327</v>
       </c>
       <c r="Q11" t="n">
-        <v>855</v>
+        <v>442</v>
       </c>
       <c r="R11" t="n">
-        <v>4209</v>
+        <v>769</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,215 +1530,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>13145981</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/13145981</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>짐타이밍</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>gymtiming1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jayoufree@gmail.com</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>043-297-0220</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqvo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>327</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>442</v>
-      </c>
-      <c r="R12" t="n">
-        <v>769</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>13145981</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/13145981</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>고트짐</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>goatgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1465-1987</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/goatgym</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vonm</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>38</v>
-      </c>
-      <c r="R13" t="n">
-        <v>102</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1290455974</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
